--- a/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
+++ b/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
   <si>
     <t>NIS</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>SISWA CONTOH 2</t>
+  </si>
+  <si>
+    <t>CICIL</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>Petunjuk Upload Tagihan</t>
@@ -80,7 +89,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -108,8 +117,17 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,6 +137,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -150,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -158,6 +182,12 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,19 +487,20 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12.854" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.567" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.995" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.854" customWidth="true" style="0"/>
+    <col min="6" max="6" width="12.854" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.569" customWidth="true" style="0"/>
+    <col min="8" max="8" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +522,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>9999999901</v>
       </c>
@@ -514,8 +548,11 @@
       <c r="G2" s="3">
         <v>250000</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>9999999902</v>
       </c>
@@ -536,6 +573,9 @@
       </c>
       <c r="G3" s="3">
         <v>400000</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -567,37 +607,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
+++ b/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
@@ -7,8 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="UPLOAD TAGIHAN" sheetId="1" r:id="rId4"/>
-    <sheet name="Keterangan" sheetId="2" r:id="rId5"/>
+    <sheet name="Data" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -16,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>NIS</t>
   </si>
@@ -36,52 +35,34 @@
     <t>ANGKATAN</t>
   </si>
   <si>
+    <t>NO_WA</t>
+  </si>
+  <si>
+    <t>KETERANGAN</t>
+  </si>
+  <si>
     <t>NOMINAL</t>
   </si>
   <si>
-    <t>SISWA CONTOH 1</t>
-  </si>
-  <si>
-    <t>RAUDHATUL JANNAH</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>2026/2027</t>
-  </si>
-  <si>
-    <t>SISWA CONTOH 2</t>
-  </si>
-  <si>
     <t>CICIL</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Petunjuk Upload Tagihan</t>
-  </si>
-  <si>
-    <t>1. Isi data pada sheet UPLOAD TAGIHAN. Jangan mengubah nama kolom baris 1.</t>
-  </si>
-  <si>
-    <t>2. Kolom wajib: NIS, NAMA, UNIT, KELAS, KELOMPOK, ANGKATAN, NOMINAL.</t>
-  </si>
-  <si>
-    <t>3. NIS harus sudah terdaftar di Data Siswa.</t>
-  </si>
-  <si>
-    <t>4. Baris contoh (NIS 99999999xx) hanya contoh, tidak ikut diimpor.</t>
-  </si>
-  <si>
-    <t>5. Simpan file saat sheet UPLOAD TAGIHAN yang aktif.</t>
-  </si>
-  <si>
-    <t>6. Contoh ini milik Sidoarjo Raudhatul Jannah, bukan sekolah lain.</t>
+    <t>CONTOH NAMA</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>2024/2025</t>
+  </si>
+  <si>
+    <t>081234567890</t>
+  </si>
+  <si>
+    <t>SPP BULAN INI</t>
   </si>
 </sst>
 </file>
@@ -89,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -99,55 +80,16 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -155,39 +97,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,157 +402,83 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.854" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.567" customWidth="true" style="0"/>
-    <col min="3" max="3" width="19.995" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.854" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12.854" customWidth="true" style="0"/>
-    <col min="7" max="7" width="11.569" customWidth="true" style="0"/>
-    <col min="8" max="8" width="12" customWidth="true" style="0"/>
+    <col min="1" max="1" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>99999999</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2">
-        <v>9999999901</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>500000</v>
+      </c>
+      <c r="J2">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3">
-        <v>250000</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2">
-        <v>9999999902</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3">
-        <v>400000</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="110" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
+++ b/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
@@ -15,12 +15,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>NIS</t>
   </si>
   <si>
     <t>NAMA</t>
+  </si>
+  <si>
+    <t>GENDER</t>
   </si>
   <si>
     <t>UNIT</t>
@@ -402,22 +405,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="6.998" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,22 +452,25 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>99999999</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -474,10 +481,13 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2">
         <v>500000</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1</v>
       </c>
     </row>

--- a/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
+++ b/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>NIS</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>CONTOH NAMA</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>SD</t>
@@ -463,26 +466,26 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>500000</v>
